--- a/Тесты_Б.7.5.xlsx
+++ b/Тесты_Б.7.5.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="14680" yWindow="660" windowWidth="14720" windowHeight="16780" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Test" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Parts" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Questions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="Z_0072DA13_AF0A_4E45_8CC6_E0F0C2CFB222_.wvu.FilterData" localSheetId="2" hidden="1">Questions!$A$3:$E$7</definedName>
@@ -856,7 +856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W102"/>
+  <dimension ref="A1:W101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="14"/>
   <cols>
     <col width="24.33203125" customWidth="1" min="1" max="1"/>
@@ -942,7 +942,7 @@
       </c>
       <c r="D2" s="50" t="inlineStr">
         <is>
-          <t>Какая категория по давлению соответствует газопроводам с давлением газа свыше 0,3 до 0,6 МПа включительно? Выберите правильный вариант ответа.</t>
+          <t>Что из перечисленного относится к материалам идентификации объектов технического регулирования? Выберите правильный вариант ответа.</t>
         </is>
       </c>
       <c r="E2" s="50" t="n">
@@ -950,7 +950,7 @@
       </c>
       <c r="F2" s="51" t="inlineStr">
         <is>
-          <t>Приложение № 1 ТР, утв. ПП РФ № 870</t>
+          <t>Тема 1.2, 2.1. п. 12 ТР, утв. ПП РФ № 870</t>
         </is>
       </c>
       <c r="G2" s="51" t="n"/>
@@ -961,7 +961,7 @@
       </c>
       <c r="I2" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -981,15 +981,15 @@
       </c>
       <c r="D3" s="51" t="inlineStr">
         <is>
-          <t>Высокого давления 2 категории.</t>
+          <t>Разрешение на ввод в эксплуатацию.</t>
         </is>
       </c>
       <c r="E3" s="51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="D4" s="51" t="inlineStr">
         <is>
-          <t>Высокого давления 1 категории.</t>
+          <t>Заключение экспертизы промышленной безопасности проектной документации на консервацию и ликвидацию сетей газораспределения и газопотребления.</t>
         </is>
       </c>
       <c r="E4" s="51" t="n">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="I4" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="D5" s="51" t="inlineStr">
         <is>
-          <t>Среднего давления.</t>
+          <t>Разрешение на строительство.</t>
         </is>
       </c>
       <c r="E5" s="51" t="n">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="I5" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1065,15 +1065,15 @@
       </c>
       <c r="D6" s="51" t="inlineStr">
         <is>
-          <t>Низкого давления.</t>
+          <t>Все перечисленное.</t>
         </is>
       </c>
       <c r="E6" s="51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="D7" s="50" t="inlineStr">
         <is>
-          <t>Каким способом допускается размещать надземные сети инженерно-технического обеспечения? Выберите правильный вариант ответа.</t>
+          <t>Использование иных материалов в качестве материалов для идентификации объектов технического регулирования: Выберите правильный вариант ответа.</t>
         </is>
       </c>
       <c r="E7" s="50" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="F7" s="51" t="inlineStr">
         <is>
-          <t>п. 6.19 СП 18.13330.2019</t>
+          <t>Тема 1.2, 2.1. п. 12 ТР, утв. ПП РФ № 870</t>
         </is>
       </c>
       <c r="G7" s="51" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="I7" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D8" s="51" t="inlineStr">
         <is>
-          <t>На опорах.</t>
+          <t>Допускается по решению проектной организации.</t>
         </is>
       </c>
       <c r="E8" s="51" t="n">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="I8" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="D9" s="51" t="inlineStr">
         <is>
-          <t>Любым способом из перечисленных.</t>
+          <t>Не допускается.</t>
         </is>
       </c>
       <c r="E9" s="51" t="n">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="I9" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D10" s="51" t="inlineStr">
         <is>
-          <t>На эстакадах.</t>
+          <t>Допускается при наличии согласования с Ростехнадзором.</t>
         </is>
       </c>
       <c r="E10" s="51" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="I10" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D11" s="51" t="inlineStr">
         <is>
-          <t>В галереях.</t>
+          <t>Допускается, если материалы подтверждают фактическое состояние объекта.</t>
         </is>
       </c>
       <c r="E11" s="51" t="n">
@@ -1224,74 +1224,74 @@
       </c>
       <c r="I11" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="51" customHeight="1">
       <c r="A12" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B12" s="51" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" s="51" t="inlineStr">
-        <is>
-          <t>Ответ</t>
-        </is>
-      </c>
-      <c r="D12" s="51" t="inlineStr">
-        <is>
-          <t>На стенах зданий и сооружений.</t>
-        </is>
-      </c>
-      <c r="E12" s="51" t="n">
-        <v>0</v>
+      <c r="B12" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="50" t="inlineStr">
+        <is>
+          <t>Вопрос</t>
+        </is>
+      </c>
+      <c r="D12" s="50" t="inlineStr">
+        <is>
+          <t>В какой форме осуществляется оценка соответствия сетей газораспределения и газопотребления требованиям Технического регламента о безопасности сетей газораспределения и газопотребления при их проектировании? Выберите правильный вариант ответа.</t>
+        </is>
+      </c>
+      <c r="E12" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="51" t="inlineStr">
+        <is>
+          <t>Тема 1.2, 2.1. п. 88 ТР, утв. ПП РФ № 870</t>
+        </is>
+      </c>
+      <c r="G12" s="51" t="n"/>
+      <c r="H12" s="50" t="inlineStr">
+        <is>
+          <t>Текст</t>
+        </is>
       </c>
       <c r="I12" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="51" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
       <c r="A13" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B13" s="50" t="n">
+      <c r="B13" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="50" t="inlineStr">
-        <is>
-          <t>Вопрос</t>
-        </is>
-      </c>
-      <c r="D13" s="50" t="inlineStr">
-        <is>
-          <t>Какую высоту следует принимать от уровня земли до низа труб (или поверхности их изоляции), прокладываемых на низких опорах на свободной территории вне проезда транспортных средств и прохода людей, при ширине группы труб от 1,5 м и более? Выберите правильный вариант ответа.</t>
-        </is>
-      </c>
-      <c r="E13" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="51" t="inlineStr">
-        <is>
-          <t>п. 6.24 СП 18.13330.2019</t>
-        </is>
-      </c>
-      <c r="G13" s="51" t="n"/>
-      <c r="H13" s="50" t="inlineStr">
-        <is>
-          <t>Текст</t>
-        </is>
+      <c r="C13" s="51" t="inlineStr">
+        <is>
+          <t>Ответ</t>
+        </is>
+      </c>
+      <c r="D13" s="51" t="inlineStr">
+        <is>
+          <t>В форме подтверждения соответствия в виде сертификации.</t>
+        </is>
+      </c>
+      <c r="E13" s="51" t="n">
+        <v>0</v>
       </c>
       <c r="I13" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="D14" s="51" t="inlineStr">
         <is>
-          <t>Не менее 0,75 м.</t>
+          <t>В форме приемки сетей газораспределения и газопотребления.</t>
         </is>
       </c>
       <c r="E14" s="51" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I14" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="D15" s="51" t="inlineStr">
         <is>
-          <t>Не менее 0,35 м.</t>
+          <t>В форме государственного контроля (надзора).</t>
         </is>
       </c>
       <c r="E15" s="51" t="n">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="I15" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1367,82 +1367,82 @@
       </c>
       <c r="D16" s="51" t="inlineStr">
         <is>
-          <t>Не менее 0,25 м.</t>
+          <t>В форме экспертизы проектной документации и результатов инженерных изысканий в соответствии с законодательством о градостроительной деятельности.</t>
         </is>
       </c>
       <c r="E16" s="51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="51" customHeight="1">
       <c r="A17" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B17" s="51" t="n">
-        <v>3</v>
-      </c>
-      <c r="C17" s="51" t="inlineStr">
-        <is>
-          <t>Ответ</t>
-        </is>
-      </c>
-      <c r="D17" s="51" t="inlineStr">
-        <is>
-          <t>Не менее 0,5 м.</t>
-        </is>
-      </c>
-      <c r="E17" s="51" t="n">
-        <v>1</v>
+      <c r="B17" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" s="50" t="inlineStr">
+        <is>
+          <t>Вопрос</t>
+        </is>
+      </c>
+      <c r="D17" s="50" t="inlineStr">
+        <is>
+          <t>Какие из перечисленных расчетов необходимо выполнять при проектировании газопроводов? Выберите правильный вариант ответа.</t>
+        </is>
+      </c>
+      <c r="E17" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="51" t="inlineStr">
+        <is>
+          <t>Тема 2.1, 2.2. п. 22 ТР, утв. ПП РФ № 870</t>
+        </is>
+      </c>
+      <c r="G17" s="51" t="n"/>
+      <c r="H17" s="50" t="inlineStr">
+        <is>
+          <t>Текст</t>
+        </is>
       </c>
       <c r="I17" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="51" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B18" s="50" t="n">
+      <c r="B18" s="51" t="n">
         <v>4</v>
       </c>
-      <c r="C18" s="50" t="inlineStr">
-        <is>
-          <t>Вопрос</t>
-        </is>
-      </c>
-      <c r="D18" s="50" t="inlineStr">
-        <is>
-          <t>Какие из перечисленных трубопроводов допускается размещать в открытых траншеях и лотках? Выберите правильный вариант ответа.</t>
-        </is>
-      </c>
-      <c r="E18" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="51" t="inlineStr">
-        <is>
-          <t>п. 6.17 СП 18.13330.2019</t>
-        </is>
-      </c>
-      <c r="G18" s="51" t="n"/>
-      <c r="H18" s="50" t="inlineStr">
-        <is>
-          <t>Текст</t>
-        </is>
+      <c r="C18" s="51" t="inlineStr">
+        <is>
+          <t>Ответ</t>
+        </is>
+      </c>
+      <c r="D18" s="51" t="inlineStr">
+        <is>
+          <t>Расчеты на прочность и герметичность газопроводов.</t>
+        </is>
+      </c>
+      <c r="E18" s="51" t="n">
+        <v>0</v>
       </c>
       <c r="I18" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="D19" s="51" t="inlineStr">
         <is>
-          <t>Не допускается размещать все перечисленные трубопроводы в открытых траншеях и лотках.</t>
+          <t>Расчеты на пропускную способность, а также расчеты на прочность и устойчивость газопроводов.</t>
         </is>
       </c>
       <c r="E19" s="51" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="I19" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="D20" s="51" t="inlineStr">
         <is>
-          <t>Трубопроводы, по которым транспортируются кислоты и щелочи.</t>
+          <t>Только гидравлический расчет газопроводов.</t>
         </is>
       </c>
       <c r="E20" s="51" t="n">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="I20" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D21" s="51" t="inlineStr">
         <is>
-          <t>Трубопроводы бытовой канализации.</t>
+          <t>Только расчеты на сейсмостойкость газопроводов.</t>
         </is>
       </c>
       <c r="E21" s="51" t="n">
@@ -1526,74 +1526,74 @@
       </c>
       <c r="I21" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="51" customHeight="1">
       <c r="A22" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B22" s="51" t="n">
-        <v>4</v>
-      </c>
-      <c r="C22" s="51" t="inlineStr">
-        <is>
-          <t>Ответ</t>
-        </is>
-      </c>
-      <c r="D22" s="51" t="inlineStr">
-        <is>
-          <t>Трубопроводы для горючих газов.</t>
-        </is>
-      </c>
-      <c r="E22" s="51" t="n">
-        <v>0</v>
+      <c r="B22" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" s="50" t="inlineStr">
+        <is>
+          <t>Вопрос</t>
+        </is>
+      </c>
+      <c r="D22" s="50" t="inlineStr">
+        <is>
+          <t>Какие условия должны обеспечивать сети газораспределения и газопотребления как объекты технического регулирования? Выберите правильный вариант ответа.</t>
+        </is>
+      </c>
+      <c r="E22" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="51" t="inlineStr">
+        <is>
+          <t>Тема 2.1. п. 14 ТР, утв. ПП РФ № 870</t>
+        </is>
+      </c>
+      <c r="G22" s="51" t="n"/>
+      <c r="H22" s="50" t="inlineStr">
+        <is>
+          <t>Текст</t>
+        </is>
       </c>
       <c r="I22" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="51" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B23" s="50" t="n">
+      <c r="B23" s="51" t="n">
         <v>5</v>
       </c>
-      <c r="C23" s="50" t="inlineStr">
-        <is>
-          <t>Вопрос</t>
-        </is>
-      </c>
-      <c r="D23" s="50" t="inlineStr">
-        <is>
-          <t>В каком случае допускается размещать надземные сети инженерно-технического обеспечения? Выберите правильный вариант ответа.</t>
-        </is>
-      </c>
-      <c r="E23" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="51" t="inlineStr">
-        <is>
-          <t>п. 6.21 СП 18.13330.2019</t>
-        </is>
-      </c>
-      <c r="G23" s="51" t="n"/>
-      <c r="H23" s="50" t="inlineStr">
-        <is>
-          <t>Текст</t>
-        </is>
+      <c r="C23" s="51" t="inlineStr">
+        <is>
+          <t>Ответ</t>
+        </is>
+      </c>
+      <c r="D23" s="51" t="inlineStr">
+        <is>
+          <t>Безопасность и энергетическую эффективность транспортирования природного газа с параметрами по давлению и расходу, определенными проектной документацией и условиями эксплуатации.</t>
+        </is>
+      </c>
+      <c r="E23" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="I23" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="D24" s="51" t="inlineStr">
         <is>
-          <t>Газопроводы горючих газов размещаются по территории складов легковоспламеняющихся и горючих жидкостей и материалов.</t>
+          <t>Пожарную безопасность транспортирования природного газа с параметрами по давлению и расходу, определенными проектной документацией.</t>
         </is>
       </c>
       <c r="E24" s="51" t="n">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="I24" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1641,15 +1641,15 @@
       </c>
       <c r="D25" s="51" t="inlineStr">
         <is>
-          <t>Не допускается ни в каком перечисленном случае.</t>
+          <t>Эффективность сжигания природного газа в газоиспользующих установках с параметрами по давлению и расходу, определенными проектной документацией.</t>
         </is>
       </c>
       <c r="E25" s="51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="D26" s="51" t="inlineStr">
         <is>
-          <t>Трубопроводы с горючими жидкими и газообразными продуктами размещаются в галереях, если смешение продуктов может вызвать взрыв или пожар.</t>
+          <t>Только пропускную способность сетей независимо от параметров давления и расхода.</t>
         </is>
       </c>
       <c r="E26" s="51" t="n">
@@ -1677,74 +1677,74 @@
       </c>
       <c r="I26" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="51" customHeight="1">
       <c r="A27" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B27" s="51" t="n">
-        <v>5</v>
-      </c>
-      <c r="C27" s="51" t="inlineStr">
-        <is>
-          <t>Ответ</t>
-        </is>
-      </c>
-      <c r="D27" s="51" t="inlineStr">
-        <is>
-          <t>Транзитные наружные трубопроводы с легковоспламеняющимися и горючими жидкостями и газами прокладывают по эстакадам, отдельно стоящим колоннам и опорам из горючих материалов.</t>
-        </is>
-      </c>
-      <c r="E27" s="51" t="n">
-        <v>0</v>
+      <c r="B27" s="50" t="n">
+        <v>6</v>
+      </c>
+      <c r="C27" s="50" t="inlineStr">
+        <is>
+          <t>Вопрос</t>
+        </is>
+      </c>
+      <c r="D27" s="50" t="inlineStr">
+        <is>
+          <t>В каком случае допускается проектирование прокладки наружных газопроводов по стенам помещений категорий А и Б по взрывопожарной опасности? Выберите правильный вариант ответа.</t>
+        </is>
+      </c>
+      <c r="E27" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="51" t="inlineStr">
+        <is>
+          <t>Тема 2.1. п. 28 ТР, утв. ПП РФ № 870</t>
+        </is>
+      </c>
+      <c r="G27" s="51" t="n"/>
+      <c r="H27" s="50" t="inlineStr">
+        <is>
+          <t>Текст</t>
+        </is>
       </c>
       <c r="I27" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="51" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
       <c r="A28" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B28" s="50" t="n">
+      <c r="B28" s="51" t="n">
         <v>6</v>
       </c>
-      <c r="C28" s="50" t="inlineStr">
-        <is>
-          <t>Вопрос</t>
-        </is>
-      </c>
-      <c r="D28" s="50" t="inlineStr">
-        <is>
-          <t>Какая категория по давлению соответствует газопроводам с давлением газа до 0,005 МПа включительно? Выберите правильный вариант ответа.</t>
-        </is>
-      </c>
-      <c r="E28" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="51" t="inlineStr">
-        <is>
-          <t>Приложение № 1 ТР, утв. ПП РФ № 870</t>
-        </is>
-      </c>
-      <c r="G28" s="51" t="n"/>
-      <c r="H28" s="50" t="inlineStr">
-        <is>
-          <t>Текст</t>
-        </is>
+      <c r="C28" s="51" t="inlineStr">
+        <is>
+          <t>Ответ</t>
+        </is>
+      </c>
+      <c r="D28" s="51" t="inlineStr">
+        <is>
+          <t>Только по зданиям газорегуляторных пунктов и пунктов учета газа.</t>
+        </is>
+      </c>
+      <c r="E28" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="I28" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="D29" s="51" t="inlineStr">
         <is>
-          <t>Среднего давления.</t>
+          <t>В случае проектирования прокладки только газопроводов низкого и среднего давления.</t>
         </is>
       </c>
       <c r="E29" s="51" t="n">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="I29" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="D30" s="51" t="inlineStr">
         <is>
-          <t>Высокого давления 1 категории.</t>
+          <t>Не допускается ни в каком случае.</t>
         </is>
       </c>
       <c r="E30" s="51" t="n">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="I30" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1820,82 +1820,82 @@
       </c>
       <c r="D31" s="51" t="inlineStr">
         <is>
-          <t>Низкого давления.</t>
+          <t>В случае проектирования прокладки газопроводов всех категорий давлений.</t>
         </is>
       </c>
       <c r="E31" s="51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="51" customHeight="1">
       <c r="A32" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B32" s="51" t="n">
-        <v>6</v>
-      </c>
-      <c r="C32" s="51" t="inlineStr">
-        <is>
-          <t>Ответ</t>
-        </is>
-      </c>
-      <c r="D32" s="51" t="inlineStr">
-        <is>
-          <t>Высокого давления 2 категории.</t>
-        </is>
-      </c>
-      <c r="E32" s="51" t="n">
-        <v>0</v>
+      <c r="B32" s="50" t="n">
+        <v>7</v>
+      </c>
+      <c r="C32" s="50" t="inlineStr">
+        <is>
+          <t>Вопрос</t>
+        </is>
+      </c>
+      <c r="D32" s="50" t="inlineStr">
+        <is>
+          <t>В каком случае допускается проектирование прокладки наружных газопроводов по железнодорожным мостам? Выберите правильный вариант ответа.</t>
+        </is>
+      </c>
+      <c r="E32" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="51" t="inlineStr">
+        <is>
+          <t>Тема 2.1. п. 28 ТР, утв. ПП РФ № 870</t>
+        </is>
+      </c>
+      <c r="G32" s="51" t="n"/>
+      <c r="H32" s="50" t="inlineStr">
+        <is>
+          <t>Текст</t>
+        </is>
       </c>
       <c r="I32" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="51" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
       <c r="A33" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B33" s="50" t="n">
+      <c r="B33" s="51" t="n">
         <v>7</v>
       </c>
-      <c r="C33" s="50" t="inlineStr">
-        <is>
-          <t>Вопрос</t>
-        </is>
-      </c>
-      <c r="D33" s="50" t="inlineStr">
-        <is>
-          <t>Размещение газопроводов с каким давлением газа разрешается совместно с другими трубопроводами и кабелями связи в каналах и тоннелях? Выберите правильный вариант ответа.</t>
-        </is>
-      </c>
-      <c r="E33" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="51" t="inlineStr">
-        <is>
-          <t>п. 6.9 СП 18.13330.2019</t>
-        </is>
-      </c>
-      <c r="G33" s="51" t="n"/>
-      <c r="H33" s="50" t="inlineStr">
-        <is>
-          <t>Текст</t>
-        </is>
+      <c r="C33" s="51" t="inlineStr">
+        <is>
+          <t>Ответ</t>
+        </is>
+      </c>
+      <c r="D33" s="51" t="inlineStr">
+        <is>
+          <t>Не допускается ни в каком случае.</t>
+        </is>
+      </c>
+      <c r="E33" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="I33" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="D34" s="51" t="inlineStr">
         <is>
-          <t>До 1,2 МПа.</t>
+          <t>В случае проектирования прокладки только газопроводов низкого и среднего давления.</t>
         </is>
       </c>
       <c r="E34" s="51" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="I34" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="D35" s="51" t="inlineStr">
         <is>
-          <t>До 1,6 МПа.</t>
+          <t>В случае проектирования прокладки только газопроводов низкого давления.</t>
         </is>
       </c>
       <c r="E35" s="51" t="n">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="I35" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="D36" s="51" t="inlineStr">
         <is>
-          <t>До 0,6 МПа.</t>
+          <t>В случае проектирования прокладки газопроводов всех категорий давлений.</t>
         </is>
       </c>
       <c r="E36" s="51" t="n">
@@ -1979,74 +1979,74 @@
       </c>
       <c r="I36" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="51" customHeight="1">
       <c r="A37" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B37" s="51" t="n">
-        <v>7</v>
-      </c>
-      <c r="C37" s="51" t="inlineStr">
-        <is>
-          <t>Ответ</t>
-        </is>
-      </c>
-      <c r="D37" s="51" t="inlineStr">
-        <is>
-          <t>Размещение газопроводов совместно с другими трубопроводами и кабелями связи в каналах и тоннелях не допускается.</t>
-        </is>
-      </c>
-      <c r="E37" s="51" t="n">
-        <v>1</v>
+      <c r="B37" s="50" t="n">
+        <v>8</v>
+      </c>
+      <c r="C37" s="50" t="inlineStr">
+        <is>
+          <t>Вопрос</t>
+        </is>
+      </c>
+      <c r="D37" s="50" t="inlineStr">
+        <is>
+          <t>Какая информация из перечисленной не указывается на опознавательных знаках, которыми обозначаются трассы подземных газопроводов? Выберите правильный вариант ответа.</t>
+        </is>
+      </c>
+      <c r="E37" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="51" t="inlineStr">
+        <is>
+          <t>Тема 2.1. п. 10 Правил охраны ГРС, утв. ПП РФ № 878</t>
+        </is>
+      </c>
+      <c r="G37" s="51" t="n"/>
+      <c r="H37" s="50" t="inlineStr">
+        <is>
+          <t>Текст</t>
+        </is>
       </c>
       <c r="I37" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="51" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
       <c r="A38" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B38" s="50" t="n">
+      <c r="B38" s="51" t="n">
         <v>8</v>
       </c>
-      <c r="C38" s="50" t="inlineStr">
-        <is>
-          <t>Вопрос</t>
-        </is>
-      </c>
-      <c r="D38" s="50" t="inlineStr">
-        <is>
-          <t>Какое из перечисленных определений соответствует понятию "газопровод сбросной"? Выберите правильный вариант ответа.</t>
-        </is>
-      </c>
-      <c r="E38" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="51" t="inlineStr">
-        <is>
-          <t>п. 7 ТР, утв. ПП РФ № 870</t>
-        </is>
-      </c>
-      <c r="G38" s="51" t="n"/>
-      <c r="H38" s="50" t="inlineStr">
-        <is>
-          <t>Текст</t>
-        </is>
+      <c r="C38" s="51" t="inlineStr">
+        <is>
+          <t>Ответ</t>
+        </is>
+      </c>
+      <c r="D38" s="51" t="inlineStr">
+        <is>
+          <t>Телефон аварийно-диспетчерской службы.</t>
+        </is>
+      </c>
+      <c r="E38" s="51" t="n">
+        <v>0</v>
       </c>
       <c r="I38" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="D39" s="51" t="inlineStr">
         <is>
-          <t>Газопровод, предназначенный для отвода природного газа от предохранительных сбросных клапанов.</t>
+          <t>Марка стали газопровода.</t>
         </is>
       </c>
       <c r="E39" s="51" t="n">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="I39" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="D40" s="51" t="inlineStr">
         <is>
-          <t>Наружный газопровод, проложенный в земле ниже уровня поверхности земли, а также по поверхности земли в насыпи (обваловании).</t>
+          <t>Расстояние от газопровода.</t>
         </is>
       </c>
       <c r="E40" s="51" t="n">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="I40" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="D41" s="51" t="inlineStr">
         <is>
-          <t>Газопровод, предназначенный для вытеснения газа или воздуха (по условиям эксплуатации) из газопроводов и технических устройств.</t>
+          <t>Глубина заложения газопровода.</t>
         </is>
       </c>
       <c r="E41" s="51" t="n">
@@ -2130,74 +2130,74 @@
       </c>
       <c r="I41" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="30" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="51" customHeight="1">
       <c r="A42" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B42" s="51" t="n">
-        <v>8</v>
-      </c>
-      <c r="C42" s="51" t="inlineStr">
-        <is>
-          <t>Ответ</t>
-        </is>
-      </c>
-      <c r="D42" s="51" t="inlineStr">
-        <is>
-          <t>Наружный газопровод, проложенный над поверхностью земли, а также по поверхности земли без насыпи (обвалования).</t>
-        </is>
-      </c>
-      <c r="E42" s="51" t="n">
-        <v>0</v>
+      <c r="B42" s="50" t="n">
+        <v>9</v>
+      </c>
+      <c r="C42" s="50" t="inlineStr">
+        <is>
+          <t>Вопрос</t>
+        </is>
+      </c>
+      <c r="D42" s="50" t="inlineStr">
+        <is>
+          <t>Какие охранные зоны установлены Правилами охраны газораспределительных сетей вдоль трасс наружных газопроводов, за исключением наружных газопроводов на вечномерзлых грунтах? Выберите правильный вариант ответа.</t>
+        </is>
+      </c>
+      <c r="E42" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="51" t="inlineStr">
+        <is>
+          <t>Тема 2.1, 3.1. п. 7 Правил охраны ГРС, утв. ПП РФ № 878</t>
+        </is>
+      </c>
+      <c r="G42" s="51" t="n"/>
+      <c r="H42" s="50" t="inlineStr">
+        <is>
+          <t>Текст</t>
+        </is>
       </c>
       <c r="I42" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="51" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
       <c r="A43" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B43" s="50" t="n">
+      <c r="B43" s="51" t="n">
         <v>9</v>
       </c>
-      <c r="C43" s="50" t="inlineStr">
-        <is>
-          <t>Вопрос</t>
-        </is>
-      </c>
-      <c r="D43" s="50" t="inlineStr">
-        <is>
-          <t>К какой категории относятся наружные и внутренние газопроводы с давлением газа в сетях газораспределения и газопотребления свыше 1,2 МПа? Выберите правильный вариант ответа.</t>
-        </is>
-      </c>
-      <c r="E43" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="51" t="inlineStr">
-        <is>
-          <t>Приложение № 1 ТР, утв. ПП РФ № 870</t>
-        </is>
-      </c>
-      <c r="G43" s="51" t="n"/>
-      <c r="H43" s="50" t="inlineStr">
-        <is>
-          <t>Текст</t>
-        </is>
+      <c r="C43" s="51" t="inlineStr">
+        <is>
+          <t>Ответ</t>
+        </is>
+      </c>
+      <c r="D43" s="51" t="inlineStr">
+        <is>
+          <t>В виде территории, ограниченной условными линиями, проходящими на расстоянии 5 м с каждой стороны газопровода.</t>
+        </is>
+      </c>
+      <c r="E43" s="51" t="n">
+        <v>0</v>
       </c>
       <c r="I43" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="D44" s="51" t="inlineStr">
         <is>
-          <t>Высокого давления 1а категории.</t>
+          <t>В виде территории, ограниченной условными линиями, проходящими на расстоянии 2 м с каждой стороны газопровода.</t>
         </is>
       </c>
       <c r="E44" s="51" t="n">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="I44" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="D45" s="51" t="inlineStr">
         <is>
-          <t>Высокого давления 2 категории.</t>
+          <t>В виде территории, ограниченной замкнутой линией, проведенной на расстоянии 5 м от границ этих объектов.</t>
         </is>
       </c>
       <c r="E45" s="51" t="n">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="I45" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="D46" s="51" t="inlineStr">
         <is>
-          <t>Высокого давления 1 категории.</t>
+          <t>В виде территории, ограниченной замкнутой линией, проведенной на расстоянии 10 м от границ этих объектов.</t>
         </is>
       </c>
       <c r="E46" s="51" t="n">
@@ -2281,74 +2281,74 @@
       </c>
       <c r="I46" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="30" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="51" customHeight="1">
       <c r="A47" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B47" s="51" t="n">
-        <v>9</v>
-      </c>
-      <c r="C47" s="51" t="inlineStr">
-        <is>
-          <t>Ответ</t>
-        </is>
-      </c>
-      <c r="D47" s="51" t="inlineStr">
-        <is>
-          <t>Среднего давления.</t>
-        </is>
-      </c>
-      <c r="E47" s="51" t="n">
-        <v>0</v>
+      <c r="B47" s="50" t="n">
+        <v>10</v>
+      </c>
+      <c r="C47" s="50" t="inlineStr">
+        <is>
+          <t>Вопрос</t>
+        </is>
+      </c>
+      <c r="D47" s="50" t="inlineStr">
+        <is>
+          <t>Какие охранные зоны установлены Правилами охраны газораспределительных сетей вдоль трасс подземных газопроводов из полиэтиленовых труб при использовании медного провода для обозначения трассы газопровода? Выберите правильный вариант ответа.</t>
+        </is>
+      </c>
+      <c r="E47" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="51" t="inlineStr">
+        <is>
+          <t>Тема 2.1. п. 7 Правил охраны ГРС, утв. ПП РФ № 878</t>
+        </is>
+      </c>
+      <c r="G47" s="51" t="n"/>
+      <c r="H47" s="50" t="inlineStr">
+        <is>
+          <t>Текст</t>
+        </is>
       </c>
       <c r="I47" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="51" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
       <c r="A48" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B48" s="50" t="n">
+      <c r="B48" s="51" t="n">
         <v>10</v>
       </c>
-      <c r="C48" s="50" t="inlineStr">
-        <is>
-          <t>Вопрос</t>
-        </is>
-      </c>
-      <c r="D48" s="50" t="inlineStr">
-        <is>
-          <t>На основании каких перечисленных условий должны определяться места размещения сбросных и продувочных газопроводов? Выберите правильный вариант ответа.</t>
-        </is>
-      </c>
-      <c r="E48" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" s="51" t="inlineStr">
-        <is>
-          <t>п. 16 ТР, утв. ПП РФ № 870</t>
-        </is>
-      </c>
-      <c r="G48" s="51" t="n"/>
-      <c r="H48" s="50" t="inlineStr">
-        <is>
-          <t>Текст</t>
-        </is>
+      <c r="C48" s="51" t="inlineStr">
+        <is>
+          <t>Ответ</t>
+        </is>
+      </c>
+      <c r="D48" s="51" t="inlineStr">
+        <is>
+          <t>В виде территории, ограниченной условными линиями, проходящими на расстоянии 3 м от газопровода со стороны провода и 2 м - с противоположной стороны.</t>
+        </is>
+      </c>
+      <c r="E48" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="I48" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="D49" s="51" t="inlineStr">
         <is>
-          <t>Максимально быстрое удаление газов из сбросных и продувочных газопроводов.</t>
+          <t>В виде территории, ограниченной условными линиями, проходящими на расстоянии 1 м с каждой стороны газопровода.</t>
         </is>
       </c>
       <c r="E49" s="51" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="I49" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="D50" s="51" t="inlineStr">
         <is>
-          <t>Максимальное рассеивание вредных веществ, при этом их концентрация в атмосфере не должна превышать более чем на 10% предельно допустимую максимальную разовую концентрацию.</t>
+          <t>В виде территории, ограниченной условными линиями, проходящими на расстоянии 3 м с каждой стороны газопровода.</t>
         </is>
       </c>
       <c r="E50" s="51" t="n">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="I50" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2424,82 +2424,82 @@
       </c>
       <c r="D51" s="51" t="inlineStr">
         <is>
-          <t>Максимальное рассеивание вредных веществ, при этом их концентрация в атмосфере не должна превышать предельно допустимую максимальную разовую концентрацию.</t>
+          <t>В виде территории, ограниченной замкнутой линией, проведенной на расстоянии 10 м с каждой стороны газопровода.</t>
         </is>
       </c>
       <c r="E51" s="51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I51" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="30" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="51" customHeight="1">
       <c r="A52" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B52" s="51" t="n">
-        <v>10</v>
-      </c>
-      <c r="C52" s="51" t="inlineStr">
-        <is>
-          <t>Ответ</t>
-        </is>
-      </c>
-      <c r="D52" s="51" t="inlineStr">
-        <is>
-          <t>Места размещения сбросных и продувочных газопроводов определяются проектом без каких-либо ограничительных условий.</t>
-        </is>
-      </c>
-      <c r="E52" s="51" t="n">
-        <v>0</v>
+      <c r="B52" s="50" t="n">
+        <v>11</v>
+      </c>
+      <c r="C52" s="50" t="inlineStr">
+        <is>
+          <t>Вопрос</t>
+        </is>
+      </c>
+      <c r="D52" s="50" t="inlineStr">
+        <is>
+          <t>На каком основании допускается производить работы, связанные с обработкой почвы на глубину более 0,3 м, собственниками, владельцами или пользователями земельных участков в охранной зоне газораспределительной сети? Выберите правильный вариант ответа.</t>
+        </is>
+      </c>
+      <c r="E52" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="51" t="inlineStr">
+        <is>
+          <t>Тема 2.1, 3.1. п. 16 Правил охраны ГРС, утв. ПП РФ № 878</t>
+        </is>
+      </c>
+      <c r="G52" s="51" t="n"/>
+      <c r="H52" s="50" t="inlineStr">
+        <is>
+          <t>Текст</t>
+        </is>
       </c>
       <c r="I52" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="51" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
       <c r="A53" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B53" s="50" t="n">
+      <c r="B53" s="51" t="n">
         <v>11</v>
       </c>
-      <c r="C53" s="50" t="inlineStr">
-        <is>
-          <t>Вопрос</t>
-        </is>
-      </c>
-      <c r="D53" s="50" t="inlineStr">
-        <is>
-          <t>Каким из перечисленных требований должна соответствовать проектная документация на сети газораспределения и газопотребления? Выберите правильный вариант ответа.</t>
-        </is>
-      </c>
-      <c r="E53" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" s="51" t="inlineStr">
-        <is>
-          <t>п. 19 ТР, утв. ПП РФ № 870</t>
-        </is>
-      </c>
-      <c r="G53" s="51" t="n"/>
-      <c r="H53" s="50" t="inlineStr">
-        <is>
-          <t>Текст</t>
-        </is>
+      <c r="C53" s="51" t="inlineStr">
+        <is>
+          <t>Ответ</t>
+        </is>
+      </c>
+      <c r="D53" s="51" t="inlineStr">
+        <is>
+          <t>На основании письменного разрешения Ростехнадзора.</t>
+        </is>
+      </c>
+      <c r="E53" s="51" t="n">
+        <v>0</v>
       </c>
       <c r="I53" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="D54" s="51" t="inlineStr">
         <is>
-          <t>Проектная документация должна соответствовать требованиям законодательства о техническом регулировании.</t>
+          <t>На основании предварительного письменного уведомления эксплуатационной организации не менее чем за 3 рабочих дня до начала работ.</t>
         </is>
       </c>
       <c r="E54" s="51" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="I54" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2547,15 +2547,15 @@
       </c>
       <c r="D55" s="51" t="inlineStr">
         <is>
-          <t>Проектная документация должна соответствовать требованиям законодательства о промышленной безопасности.</t>
+          <t>На основании письменного разрешения эксплуатационной организации газораспределительных сетей.</t>
         </is>
       </c>
       <c r="E55" s="51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2575,82 +2575,82 @@
       </c>
       <c r="D56" s="51" t="inlineStr">
         <is>
-          <t>Проектная документация должна соответствовать требованиям законодательства о градостроительной деятельности.</t>
+          <t>На основании письменного разрешения органов местного самоуправления.</t>
         </is>
       </c>
       <c r="E56" s="51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="30" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="51" customHeight="1">
       <c r="A57" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B57" s="51" t="n">
-        <v>11</v>
-      </c>
-      <c r="C57" s="51" t="inlineStr">
-        <is>
-          <t>Ответ</t>
-        </is>
-      </c>
-      <c r="D57" s="51" t="inlineStr">
-        <is>
-          <t>Проектная документация должна соответствовать всем перечисленным требованиям.</t>
-        </is>
-      </c>
-      <c r="E57" s="51" t="n">
-        <v>0</v>
+      <c r="B57" s="50" t="n">
+        <v>12</v>
+      </c>
+      <c r="C57" s="50" t="inlineStr">
+        <is>
+          <t>Вопрос</t>
+        </is>
+      </c>
+      <c r="D57" s="50" t="inlineStr">
+        <is>
+          <t>Какой нормативный документ устанавливает порядок определения границ охранных зон с особыми условиями использования территории вдоль трассы газопроводов и вокруг других объектов газораспределительной сети, которые должны быть указаны в проектной документации на сети газораспределения? Выберите правильный вариант ответа.</t>
+        </is>
+      </c>
+      <c r="E57" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="51" t="inlineStr">
+        <is>
+          <t>Тема 2.1, 3.1. п. 1 ТР, утв. ПП РФ № 870; ПП РФ № 878</t>
+        </is>
+      </c>
+      <c r="G57" s="51" t="n"/>
+      <c r="H57" s="50" t="inlineStr">
+        <is>
+          <t>Текст</t>
+        </is>
       </c>
       <c r="I57" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="51" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="30" customHeight="1">
       <c r="A58" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B58" s="50" t="n">
+      <c r="B58" s="51" t="n">
         <v>12</v>
       </c>
-      <c r="C58" s="50" t="inlineStr">
-        <is>
-          <t>Вопрос</t>
-        </is>
-      </c>
-      <c r="D58" s="50" t="inlineStr">
-        <is>
-          <t>Какие из перечисленных расчетов необходимо выполнять при проектировании газопроводов? Выберите правильный вариант ответа.</t>
-        </is>
-      </c>
-      <c r="E58" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="F58" s="51" t="inlineStr">
-        <is>
-          <t>п. 22 ТР, утв. ПП РФ № 870</t>
-        </is>
-      </c>
-      <c r="G58" s="51" t="n"/>
-      <c r="H58" s="50" t="inlineStr">
-        <is>
-          <t>Текст</t>
-        </is>
+      <c r="C58" s="51" t="inlineStr">
+        <is>
+          <t>Ответ</t>
+        </is>
+      </c>
+      <c r="D58" s="51" t="inlineStr">
+        <is>
+          <t>Технический регламент о безопасности сетей газораспределения и газопотребления.</t>
+        </is>
+      </c>
+      <c r="E58" s="51" t="n">
+        <v>0</v>
       </c>
       <c r="I58" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2670,15 +2670,15 @@
       </c>
       <c r="D59" s="51" t="inlineStr">
         <is>
-          <t>Расчеты на прочность и герметичность газопроводов.</t>
+          <t>Правила охраны газораспределительных сетей.</t>
         </is>
       </c>
       <c r="E59" s="51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2698,15 +2698,15 @@
       </c>
       <c r="D60" s="51" t="inlineStr">
         <is>
-          <t>Расчеты на пропускную способность, а также расчеты на прочность и устойчивость газопроводов.</t>
+          <t>Правила безопасности сетей газораспределения и газопотребления.</t>
         </is>
       </c>
       <c r="E60" s="51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I60" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="D61" s="51" t="inlineStr">
         <is>
-          <t>Только расчеты на прочность газопроводов.</t>
+          <t>СП 62.13330.2011*. Свод правил. Газораспределительные системы. Актуализированная редакция СНиП 42-01-2002 С изменением № 1.</t>
         </is>
       </c>
       <c r="E61" s="51" t="n">
@@ -2734,74 +2734,74 @@
       </c>
       <c r="I61" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="30" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="51" customHeight="1">
       <c r="A62" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B62" s="51" t="n">
-        <v>12</v>
-      </c>
-      <c r="C62" s="51" t="inlineStr">
-        <is>
-          <t>Ответ</t>
-        </is>
-      </c>
-      <c r="D62" s="51" t="inlineStr">
-        <is>
-          <t>Только расчеты на пропускную способность газопроводов.</t>
-        </is>
-      </c>
-      <c r="E62" s="51" t="n">
-        <v>0</v>
+      <c r="B62" s="50" t="n">
+        <v>13</v>
+      </c>
+      <c r="C62" s="50" t="inlineStr">
+        <is>
+          <t>Вопрос</t>
+        </is>
+      </c>
+      <c r="D62" s="50" t="inlineStr">
+        <is>
+          <t>Что из перечисленного должно соблюдаться при строительстве, реконструкции, монтаже и капитальном ремонте сети газораспределения и сети газопотребления? Выберите правильный вариант ответа.</t>
+        </is>
+      </c>
+      <c r="E62" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="51" t="inlineStr">
+        <is>
+          <t>Тема 3.1. п. 56 ТР, утв. ПП РФ № 870</t>
+        </is>
+      </c>
+      <c r="G62" s="51" t="n"/>
+      <c r="H62" s="50" t="inlineStr">
+        <is>
+          <t>Текст</t>
+        </is>
       </c>
       <c r="I62" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="51" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="30" customHeight="1">
       <c r="A63" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B63" s="50" t="n">
+      <c r="B63" s="51" t="n">
         <v>13</v>
       </c>
-      <c r="C63" s="50" t="inlineStr">
-        <is>
-          <t>Вопрос</t>
-        </is>
-      </c>
-      <c r="D63" s="50" t="inlineStr">
-        <is>
-          <t>В каком случае из перечисленных при пересечении надземных газопроводов высоковольтными линиями электропередачи должны быть предусмотрены защитные устройства, предотвращающие падение на газопровод электропроводов при их обрыве? Выберите правильный вариант ответа.</t>
-        </is>
-      </c>
-      <c r="E63" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="F63" s="51" t="inlineStr">
-        <is>
-          <t>п. 26 ТР, утв. ПП РФ № 870</t>
-        </is>
-      </c>
-      <c r="G63" s="51" t="n"/>
-      <c r="H63" s="50" t="inlineStr">
-        <is>
-          <t>Текст</t>
-        </is>
+      <c r="C63" s="51" t="inlineStr">
+        <is>
+          <t>Ответ</t>
+        </is>
+      </c>
+      <c r="D63" s="51" t="inlineStr">
+        <is>
+          <t>Технические решения, предусмотренные проектной документацией.</t>
+        </is>
+      </c>
+      <c r="E63" s="51" t="n">
+        <v>0</v>
       </c>
       <c r="I63" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="D64" s="51" t="inlineStr">
         <is>
-          <t>Если газопровод относится к категории 1а.</t>
+          <t>Технология строительства в соответствии с проектом производства работ или технологическими картами.</t>
         </is>
       </c>
       <c r="E64" s="51" t="n">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="I64" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="D65" s="51" t="inlineStr">
         <is>
-          <t>При прокладке газопроводов на территории городских поселений.</t>
+          <t>Требования эксплуатационной документации изготовителей газоиспользующего оборудования, технических и технологических устройств, труб, материалов и соединительных деталей.</t>
         </is>
       </c>
       <c r="E65" s="51" t="n">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="I65" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2877,82 +2877,82 @@
       </c>
       <c r="D66" s="51" t="inlineStr">
         <is>
-          <t>В случае особых климатических и гидрогеологических условий, а также в зависимости от внешних воздействий на газопроводы.</t>
+          <t>Должно соблюдаться все перечисленное.</t>
         </is>
       </c>
       <c r="E66" s="51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="30" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="51" customHeight="1">
       <c r="A67" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B67" s="51" t="n">
-        <v>13</v>
-      </c>
-      <c r="C67" s="51" t="inlineStr">
-        <is>
-          <t>Ответ</t>
-        </is>
-      </c>
-      <c r="D67" s="51" t="inlineStr">
-        <is>
-          <t>При напряжении высоковольтных линий свыше 1 кВ.</t>
-        </is>
-      </c>
-      <c r="E67" s="51" t="n">
-        <v>1</v>
+      <c r="B67" s="50" t="n">
+        <v>14</v>
+      </c>
+      <c r="C67" s="50" t="inlineStr">
+        <is>
+          <t>Вопрос</t>
+        </is>
+      </c>
+      <c r="D67" s="50" t="inlineStr">
+        <is>
+          <t>На основании каких документов осуществляются эксплуатация, включая ремонт и техническое перевооружение, консервация и ликвидация сетей газораспределения и газопотребления? Выберите правильный вариант ответа.</t>
+        </is>
+      </c>
+      <c r="E67" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="51" t="inlineStr">
+        <is>
+          <t>Тема 1.1, 1.2, 3.2. п. 4 ФНП, утв. приказом Ростехнадзора № 531</t>
+        </is>
+      </c>
+      <c r="G67" s="51" t="n"/>
+      <c r="H67" s="50" t="inlineStr">
+        <is>
+          <t>Текст</t>
+        </is>
       </c>
       <c r="I67" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="51" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="30" customHeight="1">
       <c r="A68" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B68" s="50" t="n">
+      <c r="B68" s="51" t="n">
         <v>14</v>
       </c>
-      <c r="C68" s="50" t="inlineStr">
-        <is>
-          <t>Вопрос</t>
-        </is>
-      </c>
-      <c r="D68" s="50" t="inlineStr">
-        <is>
-          <t>Какие из перечисленных проектных решений, предусматриваемых в случае пересечения надземных газопроводов с высоковольтными линиями электропередачи, указаны верно? Выберите правильный вариант ответа.</t>
-        </is>
-      </c>
-      <c r="E68" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="F68" s="51" t="inlineStr">
-        <is>
-          <t>п. 26 ТР, утв. ПП РФ № 870</t>
-        </is>
-      </c>
-      <c r="G68" s="51" t="n"/>
-      <c r="H68" s="50" t="inlineStr">
-        <is>
-          <t>Текст</t>
-        </is>
+      <c r="C68" s="51" t="inlineStr">
+        <is>
+          <t>Ответ</t>
+        </is>
+      </c>
+      <c r="D68" s="51" t="inlineStr">
+        <is>
+          <t>Всех перечисленных документов.</t>
+        </is>
+      </c>
+      <c r="E68" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="I68" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2972,15 +2972,15 @@
       </c>
       <c r="D69" s="51" t="inlineStr">
         <is>
-          <t>При напряжении линии электропередачи, превышающем 1 кВ, должны быть предусмотрены защитные устройства, предотвращающие падение на газопровод электропроводов при их обрыве, а также защитные устройства от падения опор линий электропередачи.</t>
+          <t>Правил безопасности сетей газораспределения и газопотребления.</t>
         </is>
       </c>
       <c r="E69" s="51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I69" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="D70" s="51" t="inlineStr">
         <is>
-          <t>При любом напряжении линии электропередачи должны быть предусмотрены защитные устройства, предотвращающие падение на газопровод электропроводов при их обрыве, а также защитные устройства от падения опор линий электропередачи.</t>
+          <t>Федерального закона от 21.07.1997 № 116-ФЗ «О промышленной безопасности опасных производственных объектов».</t>
         </is>
       </c>
       <c r="E70" s="51" t="n">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="I70" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="D71" s="51" t="inlineStr">
         <is>
-          <t>Глубину прокладки газопровода при пересечении с линией электропередачи следует принимать исходя из расчета исключения возможности повреждения линии электропередачи при подъеме уровня воды.</t>
+          <t>Технического регламента о безопасности сетей газораспределения и газопотребления.</t>
         </is>
       </c>
       <c r="E71" s="51" t="n">
@@ -3036,74 +3036,74 @@
       </c>
       <c r="I71" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="30" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="51" customHeight="1">
       <c r="A72" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B72" s="51" t="n">
-        <v>14</v>
-      </c>
-      <c r="C72" s="51" t="inlineStr">
-        <is>
-          <t>Ответ</t>
-        </is>
-      </c>
-      <c r="D72" s="51" t="inlineStr">
-        <is>
-          <t>При напряжении линии электропередачи, превышающем 1 кВ, должно быть предусмотрено либо применение диэлектрических футляров на газопроводах, либо подземная прокладка газопровода на участке пересечения.</t>
-        </is>
-      </c>
-      <c r="E72" s="51" t="n">
-        <v>0</v>
+      <c r="B72" s="50" t="n">
+        <v>15</v>
+      </c>
+      <c r="C72" s="50" t="inlineStr">
+        <is>
+          <t>Вопрос</t>
+        </is>
+      </c>
+      <c r="D72" s="50" t="inlineStr">
+        <is>
+          <t>Какие из перечисленных требований к проектированию подземного участка газопровода указаны верно? Выберите 2 варианта ответа.</t>
+        </is>
+      </c>
+      <c r="E72" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="F72" s="51" t="inlineStr">
+        <is>
+          <t>Тема 2.2. п. 33 ТР, утв. ПП РФ № 870. Нужно отметить 2 ответа</t>
+        </is>
+      </c>
+      <c r="G72" s="51" t="n"/>
+      <c r="H72" s="50" t="inlineStr">
+        <is>
+          <t>Текст</t>
+        </is>
       </c>
       <c r="I72" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="51" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="30" customHeight="1">
       <c r="A73" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B73" s="50" t="n">
+      <c r="B73" s="51" t="n">
         <v>15</v>
       </c>
-      <c r="C73" s="50" t="inlineStr">
-        <is>
-          <t>Вопрос</t>
-        </is>
-      </c>
-      <c r="D73" s="50" t="inlineStr">
-        <is>
-          <t>В каком случае допускается проектирование прокладки наружных газопроводов по стенам помещений категорий А и Б по взрывопожарной опасности? Выберите правильный вариант ответа.</t>
-        </is>
-      </c>
-      <c r="E73" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="F73" s="51" t="inlineStr">
-        <is>
-          <t>п. 28 ТР, утв. ПП РФ № 870</t>
-        </is>
-      </c>
-      <c r="G73" s="51" t="n"/>
-      <c r="H73" s="50" t="inlineStr">
-        <is>
-          <t>Текст</t>
-        </is>
+      <c r="C73" s="51" t="inlineStr">
+        <is>
+          <t>Ответ</t>
+        </is>
+      </c>
+      <c r="D73" s="51" t="inlineStr">
+        <is>
+          <t>На оползневых участках подземный газопровод должен проектироваться на 1 м ниже плоскости скольжения оползня.</t>
+        </is>
+      </c>
+      <c r="E73" s="51" t="n">
+        <v>0</v>
       </c>
       <c r="I73" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3123,15 +3123,15 @@
       </c>
       <c r="D74" s="51" t="inlineStr">
         <is>
-          <t>Только по зданиям газорегуляторных пунктов и пунктов учета газа.</t>
+          <t>На подверженных эрозии участках подземный газопровод должен проектироваться на 1 м ниже границы прогнозируемого размыва.</t>
         </is>
       </c>
       <c r="E74" s="51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I74" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3151,15 +3151,15 @@
       </c>
       <c r="D75" s="51" t="inlineStr">
         <is>
-          <t>В случае проектирования прокладки только газопроводов низкого и среднего давления.</t>
+          <t>На оползневых участках подземный газопровод должен проектироваться на 0,5 м ниже плоскости скольжения оползня.</t>
         </is>
       </c>
       <c r="E75" s="51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3179,82 +3179,82 @@
       </c>
       <c r="D76" s="51" t="inlineStr">
         <is>
-          <t>Не допускается ни в каком случае.</t>
+          <t>На подверженных эрозии участках подземный газопровод должен проектироваться на 0,5 м ниже границы прогнозируемого размыва.</t>
         </is>
       </c>
       <c r="E76" s="51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="30" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="51" customHeight="1">
       <c r="A77" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B77" s="51" t="n">
-        <v>15</v>
-      </c>
-      <c r="C77" s="51" t="inlineStr">
-        <is>
-          <t>Ответ</t>
-        </is>
-      </c>
-      <c r="D77" s="51" t="inlineStr">
-        <is>
-          <t>Допускается во всех перечисленных случаях.</t>
-        </is>
-      </c>
-      <c r="E77" s="51" t="n">
-        <v>0</v>
+      <c r="B77" s="50" t="n">
+        <v>16</v>
+      </c>
+      <c r="C77" s="50" t="inlineStr">
+        <is>
+          <t>Вопрос</t>
+        </is>
+      </c>
+      <c r="D77" s="50" t="inlineStr">
+        <is>
+          <t>Какое давление природного газа должно быть на входе в газорегуляторную установку? Выберите правильный вариант ответа.</t>
+        </is>
+      </c>
+      <c r="E77" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" s="51" t="inlineStr">
+        <is>
+          <t>Тема 2.2. п. 42 ТР, утв. ПП РФ № 870</t>
+        </is>
+      </c>
+      <c r="G77" s="51" t="n"/>
+      <c r="H77" s="50" t="inlineStr">
+        <is>
+          <t>Текст</t>
+        </is>
       </c>
       <c r="I77" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="51" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="30" customHeight="1">
       <c r="A78" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B78" s="50" t="n">
+      <c r="B78" s="51" t="n">
         <v>16</v>
       </c>
-      <c r="C78" s="50" t="inlineStr">
-        <is>
-          <t>Вопрос</t>
-        </is>
-      </c>
-      <c r="D78" s="50" t="inlineStr">
-        <is>
-          <t>В каком случае допускается проектирование прокладки наружных газопроводов по железнодорожным мостам? Выберите правильный вариант ответа.</t>
-        </is>
-      </c>
-      <c r="E78" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="F78" s="51" t="inlineStr">
-        <is>
-          <t>п. 28 ТР, утв. ПП РФ № 870</t>
-        </is>
-      </c>
-      <c r="G78" s="51" t="n"/>
-      <c r="H78" s="50" t="inlineStr">
-        <is>
-          <t>Текст</t>
-        </is>
+      <c r="C78" s="51" t="inlineStr">
+        <is>
+          <t>Ответ</t>
+        </is>
+      </c>
+      <c r="D78" s="51" t="inlineStr">
+        <is>
+          <t>Не должно превышать 0,6 МПа.</t>
+        </is>
+      </c>
+      <c r="E78" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="I78" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3274,15 +3274,15 @@
       </c>
       <c r="D79" s="51" t="inlineStr">
         <is>
-          <t>Не допускается ни в каком случае.</t>
+          <t>Не должно превышать 1,2 МПа.</t>
         </is>
       </c>
       <c r="E79" s="51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I79" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="D80" s="51" t="inlineStr">
         <is>
-          <t>В случае проектирования прокладки только газопроводов низкого и среднего давления.</t>
+          <t>Не должно превышать 0,3 МПа.</t>
         </is>
       </c>
       <c r="E80" s="51" t="n">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="I80" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3330,7 +3330,7 @@
       </c>
       <c r="D81" s="51" t="inlineStr">
         <is>
-          <t>В случае проектирования прокладки только газопроводов низкого давления.</t>
+          <t>Не должно превышать 1,6 МПа.</t>
         </is>
       </c>
       <c r="E81" s="51" t="n">
@@ -3338,74 +3338,74 @@
       </c>
       <c r="I81" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="30" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="51" customHeight="1">
       <c r="A82" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B82" s="51" t="n">
-        <v>16</v>
-      </c>
-      <c r="C82" s="51" t="inlineStr">
-        <is>
-          <t>Ответ</t>
-        </is>
-      </c>
-      <c r="D82" s="51" t="inlineStr">
-        <is>
-          <t>В случае проектирования прокладки газопроводов всех категорий давлений.</t>
-        </is>
-      </c>
-      <c r="E82" s="51" t="n">
-        <v>0</v>
+      <c r="B82" s="50" t="n">
+        <v>17</v>
+      </c>
+      <c r="C82" s="50" t="inlineStr">
+        <is>
+          <t>Вопрос</t>
+        </is>
+      </c>
+      <c r="D82" s="50" t="inlineStr">
+        <is>
+          <t>Какой воздухообмен обеспечивается вентиляцией для помещений котельных, в которых установлено газоиспользующее оборудование, с постоянным присутствием обслуживающего персонала? Выберите правильный вариант ответа.</t>
+        </is>
+      </c>
+      <c r="E82" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" s="51" t="inlineStr">
+        <is>
+          <t>Тема 2.2. п. 55 ТР, утв. ПП РФ № 870</t>
+        </is>
+      </c>
+      <c r="G82" s="51" t="n"/>
+      <c r="H82" s="50" t="inlineStr">
+        <is>
+          <t>Текст</t>
+        </is>
       </c>
       <c r="I82" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="51" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="30" customHeight="1">
       <c r="A83" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B83" s="50" t="n">
+      <c r="B83" s="51" t="n">
         <v>17</v>
       </c>
-      <c r="C83" s="50" t="inlineStr">
-        <is>
-          <t>Вопрос</t>
-        </is>
-      </c>
-      <c r="D83" s="50" t="inlineStr">
-        <is>
-          <t>Какое из перечисленных определений соответствует понятию "газопровод продувочный"? Выберите правильный вариант ответа.</t>
-        </is>
-      </c>
-      <c r="E83" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="F83" s="51" t="inlineStr">
-        <is>
-          <t>п. 7 ТР, утв. ПП РФ № 870</t>
-        </is>
-      </c>
-      <c r="G83" s="51" t="n"/>
-      <c r="H83" s="50" t="inlineStr">
-        <is>
-          <t>Текст</t>
-        </is>
+      <c r="C83" s="51" t="inlineStr">
+        <is>
+          <t>Ответ</t>
+        </is>
+      </c>
+      <c r="D83" s="51" t="inlineStr">
+        <is>
+          <t>Не менее пятикратного в час.</t>
+        </is>
+      </c>
+      <c r="E83" s="51" t="n">
+        <v>0</v>
       </c>
       <c r="I83" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3425,7 +3425,7 @@
       </c>
       <c r="D84" s="51" t="inlineStr">
         <is>
-          <t>Газопровод, предназначенный для отвода природного газа от предохранительных сбросных клапанов.</t>
+          <t>Не менее шестикратного в час.</t>
         </is>
       </c>
       <c r="E84" s="51" t="n">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="I84" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3453,15 +3453,15 @@
       </c>
       <c r="D85" s="51" t="inlineStr">
         <is>
-          <t>Газопровод, предназначенный для вытеснения газа или воздуха (по условиям эксплуатации) из газопроводов и технических устройств.</t>
+          <t>Не менее четырехкратного в час.</t>
         </is>
       </c>
       <c r="E85" s="51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I85" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3481,82 +3481,82 @@
       </c>
       <c r="D86" s="51" t="inlineStr">
         <is>
-          <t>Наружный газопровод, проложенный в земле ниже уровня поверхности земли, а также по поверхности земли в насыпи (обваловании).</t>
+          <t>Не менее трехкратного в час.</t>
         </is>
       </c>
       <c r="E86" s="51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I86" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="30" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="51" customHeight="1">
       <c r="A87" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B87" s="51" t="n">
-        <v>17</v>
-      </c>
-      <c r="C87" s="51" t="inlineStr">
-        <is>
-          <t>Ответ</t>
-        </is>
-      </c>
-      <c r="D87" s="51" t="inlineStr">
-        <is>
-          <t>Наружный газопровод, проложенный над поверхностью земли, а также по поверхности земли без насыпи (обвалования).</t>
-        </is>
-      </c>
-      <c r="E87" s="51" t="n">
-        <v>0</v>
+      <c r="B87" s="50" t="n">
+        <v>18</v>
+      </c>
+      <c r="C87" s="50" t="inlineStr">
+        <is>
+          <t>Вопрос</t>
+        </is>
+      </c>
+      <c r="D87" s="50" t="inlineStr">
+        <is>
+          <t>Каким оборудованием должны оснащаться технологические устройства систем газораспределения и газопотребления? Выберите правильный вариант ответа.</t>
+        </is>
+      </c>
+      <c r="E87" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" s="51" t="inlineStr">
+        <is>
+          <t>Тема 2.2. п. 35 ТР, утв. ПП РФ № 870</t>
+        </is>
+      </c>
+      <c r="G87" s="51" t="n"/>
+      <c r="H87" s="50" t="inlineStr">
+        <is>
+          <t>Текст</t>
+        </is>
       </c>
       <c r="I87" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="51" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="30" customHeight="1">
       <c r="A88" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B88" s="50" t="n">
+      <c r="B88" s="51" t="n">
         <v>18</v>
       </c>
-      <c r="C88" s="50" t="inlineStr">
-        <is>
-          <t>Вопрос</t>
-        </is>
-      </c>
-      <c r="D88" s="50" t="inlineStr">
-        <is>
-          <t>Какая категория по давлению соответствует газопроводам с давлением газа свыше 0,6 до 1,2 МПа включительно? Выберите правильный вариант ответа.</t>
-        </is>
-      </c>
-      <c r="E88" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="F88" s="51" t="inlineStr">
-        <is>
-          <t>Приложение № 1 ТР, утв. ПП РФ № 870</t>
-        </is>
-      </c>
-      <c r="G88" s="51" t="n"/>
-      <c r="H88" s="50" t="inlineStr">
-        <is>
-          <t>Текст</t>
-        </is>
+      <c r="C88" s="51" t="inlineStr">
+        <is>
+          <t>Ответ</t>
+        </is>
+      </c>
+      <c r="D88" s="51" t="inlineStr">
+        <is>
+          <t>Шкафом из легкосбрасываемых конструкций.</t>
+        </is>
+      </c>
+      <c r="E88" s="51" t="n">
+        <v>0</v>
       </c>
       <c r="I88" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3576,15 +3576,15 @@
       </c>
       <c r="D89" s="51" t="inlineStr">
         <is>
-          <t>Высокого давления 1а категории.</t>
+          <t>Молниезащитой, заземлением и вентиляцией.</t>
         </is>
       </c>
       <c r="E89" s="51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I89" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3604,15 +3604,15 @@
       </c>
       <c r="D90" s="51" t="inlineStr">
         <is>
-          <t>Высокого давления 1 категории.</t>
+          <t>Ограждающими конструкциями, обеспечивающими этим устройствам III-V степени огнестойкости и класс конструктивной пожарной опасности С1.</t>
         </is>
       </c>
       <c r="E90" s="51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I90" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="D91" s="51" t="inlineStr">
         <is>
-          <t>Высокого давления 2 категории.</t>
+          <t>Только вентиляцией без молниезащиты и заземления.</t>
         </is>
       </c>
       <c r="E91" s="51" t="n">
@@ -3640,74 +3640,74 @@
       </c>
       <c r="I91" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="30" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="51" customHeight="1">
       <c r="A92" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B92" s="51" t="n">
-        <v>18</v>
-      </c>
-      <c r="C92" s="51" t="inlineStr">
-        <is>
-          <t>Ответ</t>
-        </is>
-      </c>
-      <c r="D92" s="51" t="inlineStr">
-        <is>
-          <t>Среднего давления.</t>
-        </is>
-      </c>
-      <c r="E92" s="51" t="n">
-        <v>0</v>
+      <c r="B92" s="50" t="n">
+        <v>19</v>
+      </c>
+      <c r="C92" s="50" t="inlineStr">
+        <is>
+          <t>Вопрос</t>
+        </is>
+      </c>
+      <c r="D92" s="50" t="inlineStr">
+        <is>
+          <t>Какие перечисленные мероприятия предусматриваются при консервации сетей газораспределения и сетей газопотребления? Выберите правильный вариант ответа.</t>
+        </is>
+      </c>
+      <c r="E92" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" s="51" t="inlineStr">
+        <is>
+          <t>Тема 3.2. п. 82 ТР, утв. ПП РФ № 870</t>
+        </is>
+      </c>
+      <c r="G92" s="51" t="n"/>
+      <c r="H92" s="50" t="inlineStr">
+        <is>
+          <t>Текст</t>
+        </is>
       </c>
       <c r="I92" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="51" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="30" customHeight="1">
       <c r="A93" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B93" s="50" t="n">
+      <c r="B93" s="51" t="n">
         <v>19</v>
       </c>
-      <c r="C93" s="50" t="inlineStr">
-        <is>
-          <t>Вопрос</t>
-        </is>
-      </c>
-      <c r="D93" s="50" t="inlineStr">
-        <is>
-          <t>Какая категория по давлению соответствует газопроводам с давлением газа свыше 0,005 до 0,3 МПа включительно? Выберите правильный вариант ответа.</t>
-        </is>
-      </c>
-      <c r="E93" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="F93" s="51" t="inlineStr">
-        <is>
-          <t>Приложение № 1 ТР, утв. ПП РФ № 870</t>
-        </is>
-      </c>
-      <c r="G93" s="51" t="n"/>
-      <c r="H93" s="50" t="inlineStr">
-        <is>
-          <t>Текст</t>
-        </is>
+      <c r="C93" s="51" t="inlineStr">
+        <is>
+          <t>Ответ</t>
+        </is>
+      </c>
+      <c r="D93" s="51" t="inlineStr">
+        <is>
+          <t>Мероприятия, обеспечивающие их материальную сохранность и предотвращение их разрушения.</t>
+        </is>
+      </c>
+      <c r="E93" s="51" t="n">
+        <v>0</v>
       </c>
       <c r="I93" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="D94" s="51" t="inlineStr">
         <is>
-          <t>Низкого давления.</t>
+          <t>Мероприятия, обеспечивающие восстановление их работоспособности после расконсервации.</t>
         </is>
       </c>
       <c r="E94" s="51" t="n">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="I94" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="D95" s="51" t="inlineStr">
         <is>
-          <t>Среднего давления.</t>
+          <t>Все перечисленные мероприятия.</t>
         </is>
       </c>
       <c r="E95" s="51" t="n">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="I95" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="D96" s="51" t="inlineStr">
         <is>
-          <t>Высокого давления 2 категории.</t>
+          <t>Мероприятия, обеспечивающие их промышленную и экологическую безопасность.</t>
         </is>
       </c>
       <c r="E96" s="51" t="n">
@@ -3791,74 +3791,74 @@
       </c>
       <c r="I96" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="30" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="51" customHeight="1">
       <c r="A97" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B97" s="51" t="n">
-        <v>19</v>
-      </c>
-      <c r="C97" s="51" t="inlineStr">
-        <is>
-          <t>Ответ</t>
-        </is>
-      </c>
-      <c r="D97" s="51" t="inlineStr">
-        <is>
-          <t>Высокого давления 1 категории.</t>
-        </is>
-      </c>
-      <c r="E97" s="51" t="n">
-        <v>0</v>
+      <c r="B97" s="50" t="n">
+        <v>20</v>
+      </c>
+      <c r="C97" s="50" t="inlineStr">
+        <is>
+          <t>Вопрос</t>
+        </is>
+      </c>
+      <c r="D97" s="50" t="inlineStr">
+        <is>
+          <t>На основании каких перечисленных условий должны определяться места размещения сбросных и продувочных газопроводов? Выберите правильный вариант ответа.</t>
+        </is>
+      </c>
+      <c r="E97" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" s="51" t="inlineStr">
+        <is>
+          <t>Тема 2.1. п. 16 ТР, утв. ПП РФ № 870</t>
+        </is>
+      </c>
+      <c r="G97" s="51" t="n"/>
+      <c r="H97" s="50" t="inlineStr">
+        <is>
+          <t>Текст</t>
+        </is>
       </c>
       <c r="I97" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="51" customHeight="1">
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="30" customHeight="1">
       <c r="A98" s="49" t="inlineStr">
         <is>
           <t>Итоговое тестирование</t>
         </is>
       </c>
-      <c r="B98" s="50" t="n">
+      <c r="B98" s="51" t="n">
         <v>20</v>
       </c>
-      <c r="C98" s="50" t="inlineStr">
-        <is>
-          <t>Вопрос</t>
-        </is>
-      </c>
-      <c r="D98" s="50" t="inlineStr">
-        <is>
-          <t>Использование иных материалов в качестве материалов для идентификации объектов технического регулирования: Выберите правильный вариант ответа.</t>
-        </is>
-      </c>
-      <c r="E98" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="F98" s="51" t="inlineStr">
-        <is>
-          <t>ТР, утв. ПП РФ № 870 (материалы идентификации)</t>
-        </is>
-      </c>
-      <c r="G98" s="51" t="n"/>
-      <c r="H98" s="50" t="inlineStr">
-        <is>
-          <t>Текст</t>
-        </is>
+      <c r="C98" s="51" t="inlineStr">
+        <is>
+          <t>Ответ</t>
+        </is>
+      </c>
+      <c r="D98" s="51" t="inlineStr">
+        <is>
+          <t>Максимально быстрое удаление газов из сбросных и продувочных газопроводов.</t>
+        </is>
+      </c>
+      <c r="E98" s="51" t="n">
+        <v>0</v>
       </c>
       <c r="I98" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D99" s="51" t="inlineStr">
         <is>
-          <t>Допускается по решению проектной организации.</t>
+          <t>Максимальное рассеивание вредных веществ, при этом их концентрация в атмосфере не должна превышать более чем на 10% предельно допустимую максимальную разовую концентрацию.</t>
         </is>
       </c>
       <c r="E99" s="51" t="n">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="I99" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="D100" s="51" t="inlineStr">
         <is>
-          <t>Не допускается.</t>
+          <t>Максимальное рассеивание вредных веществ, при этом их концентрация в атмосфере не должна превышать предельно допустимую максимальную разовую концентрацию.</t>
         </is>
       </c>
       <c r="E100" s="51" t="n">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="I100" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="D101" s="51" t="inlineStr">
         <is>
-          <t>Допускается при наличии согласования с Ростехнадзором.</t>
+          <t>Места размещения сбросных и продувочных газопроводов определяются проектом без каких-либо ограничительных условий.</t>
         </is>
       </c>
       <c r="E101" s="51" t="n">
@@ -3942,35 +3942,7 @@
       </c>
       <c r="I101" s="51" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="30" customHeight="1">
-      <c r="A102" s="49" t="inlineStr">
-        <is>
-          <t>Итоговое тестирование</t>
-        </is>
-      </c>
-      <c r="B102" s="51" t="n">
-        <v>20</v>
-      </c>
-      <c r="C102" s="51" t="inlineStr">
-        <is>
-          <t>Ответ</t>
-        </is>
-      </c>
-      <c r="D102" s="51" t="inlineStr">
-        <is>
-          <t>Допускается, если материалы подтверждают фактическое состояние объекта.</t>
-        </is>
-      </c>
-      <c r="E102" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" s="51" t="inlineStr">
-        <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
